--- a/EX_GAS_Config/ProjectConfigTable/exgas_config/Datas/#exgas.attributeSet.xlsx
+++ b/EX_GAS_Config/ProjectConfigTable/exgas_config/Datas/#exgas.attributeSet.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K31"/>
+  <dimension ref="A1:K35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.8"/>
   <cols>
     <col width="26.5546875" customWidth="1" min="3" max="3"/>
@@ -812,27 +812,17 @@
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>Bullet</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>子弹飞行物用的属性集</t>
-        </is>
-      </c>
+      <c r="B14" s="2" t="n"/>
+      <c r="C14" s="2" t="n"/>
+      <c r="D14" s="2" t="n"/>
       <c r="E14" s="2" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="F14" s="2" t="n"/>
-      <c r="G14" t="n">
-        <v>100</v>
-      </c>
-      <c r="H14" t="n">
+      <c r="G14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I14" s="2" t="n">
@@ -850,19 +840,20 @@
       </c>
     </row>
     <row r="15">
+      <c r="B15" s="2" t="n"/>
       <c r="C15" s="2" t="n"/>
       <c r="D15" s="2" t="n"/>
       <c r="E15" s="2" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F15" s="2" t="n"/>
-      <c r="G15" t="n">
-        <v>10</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
+      <c r="G15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" s="2" t="n">
         <v>999</v>
       </c>
       <c r="J15" t="inlineStr">
@@ -877,33 +868,134 @@
       </c>
     </row>
     <row r="16">
+      <c r="B16" s="2" t="n"/>
       <c r="C16" s="2" t="n"/>
       <c r="D16" s="2" t="n"/>
-      <c r="E16" s="2" t="n"/>
+      <c r="E16" s="2" t="n">
+        <v>13</v>
+      </c>
       <c r="F16" s="2" t="n"/>
-      <c r="I16" s="2" t="n"/>
+      <c r="G16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" s="2" t="n">
+        <v>999</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
     </row>
     <row r="17">
+      <c r="B17" s="2" t="n"/>
       <c r="C17" s="2" t="n"/>
       <c r="D17" s="2" t="n"/>
+      <c r="E17" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="F17" s="2" t="n"/>
+      <c r="G17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" s="2" t="n">
+        <v>999</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="B18" s="2" t="n"/>
-      <c r="C18" s="2" t="n"/>
-      <c r="D18" s="2" t="n"/>
+      <c r="B18" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Bullet</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>子弹飞行物用的属性集</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F18" s="2" t="n"/>
+      <c r="G18" t="n">
+        <v>100</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" s="2" t="n">
+        <v>999</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="B19" s="2" t="n"/>
       <c r="C19" s="2" t="n"/>
       <c r="D19" s="2" t="n"/>
+      <c r="E19" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F19" s="2" t="n"/>
+      <c r="G19" t="n">
+        <v>10</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>999</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="B20" s="2" t="n"/>
       <c r="C20" s="2" t="n"/>
       <c r="D20" s="2" t="n"/>
+      <c r="E20" s="2" t="n"/>
+      <c r="F20" s="2" t="n"/>
+      <c r="I20" s="2" t="n"/>
     </row>
     <row r="21">
-      <c r="B21" s="2" t="n"/>
       <c r="C21" s="2" t="n"/>
       <c r="D21" s="2" t="n"/>
     </row>
@@ -934,16 +1026,36 @@
     </row>
     <row r="27">
       <c r="B27" s="2" t="n"/>
+      <c r="C27" s="2" t="n"/>
+      <c r="D27" s="2" t="n"/>
     </row>
     <row r="28">
       <c r="B28" s="2" t="n"/>
-    </row>
-    <row r="29"/>
+      <c r="C28" s="2" t="n"/>
+      <c r="D28" s="2" t="n"/>
+    </row>
+    <row r="29">
+      <c r="B29" s="2" t="n"/>
+      <c r="C29" s="2" t="n"/>
+      <c r="D29" s="2" t="n"/>
+    </row>
     <row r="30">
       <c r="B30" s="2" t="n"/>
+      <c r="C30" s="2" t="n"/>
+      <c r="D30" s="2" t="n"/>
     </row>
     <row r="31">
       <c r="B31" s="2" t="n"/>
+    </row>
+    <row r="32">
+      <c r="B32" s="2" t="n"/>
+    </row>
+    <row r="33"/>
+    <row r="34">
+      <c r="B34" s="2" t="n"/>
+    </row>
+    <row r="35">
+      <c r="B35" s="2" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
